--- a/output/pdf_financials_xlsx/BRTA.H.xlsx
+++ b/output/pdf_financials_xlsx/BRTA.H.xlsx
@@ -4645,13 +4645,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.040649</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.040649</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.08236400000000001</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0.08236400000000001</v>
@@ -10758,7 +10758,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -10984,7 +10988,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -11210,7 +11218,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>0.040649</v>
       </c>

--- a/output/pdf_financials_xlsx/BRTA.H.xlsx
+++ b/output/pdf_financials_xlsx/BRTA.H.xlsx
@@ -1999,40 +1999,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.149076</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.029968</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001185</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.001487</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.002725</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.005095</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.069242</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.002627</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000561</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.004186</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000725</v>
       </c>
     </row>
     <row r="35">
@@ -2085,40 +2085,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.149076</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.029968</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001185</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.001487</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.002725</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.005095</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.069242</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.002627</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000561</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.004186</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000725</v>
       </c>
     </row>
     <row r="37">
@@ -2601,40 +2601,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.149076</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.033001</v>
+        <v>0.003033</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.001185</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.001598</v>
+        <v>0.000111</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.002725</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.005095</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.069242</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.003127</v>
+        <v>0.0005</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.001086</v>
+        <v>0.000525</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.005289</v>
+        <v>0.001103</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.000725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
@@ -20240,11 +20240,7 @@
           <t>General and administrative fees $</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" s="5" t="n">
         <v>0.009174</v>
       </c>

--- a/output/pdf_financials_xlsx/BRTA.H.xlsx
+++ b/output/pdf_financials_xlsx/BRTA.H.xlsx
@@ -615,10 +615,8 @@
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>0</v>
@@ -723,10 +721,8 @@
       <c r="G7" s="3" t="n">
         <v>0.015999</v>
       </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H7" s="3" t="n">
+        <v>0.016243</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.018058</v>
@@ -768,10 +764,8 @@
       <c r="G8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -813,10 +807,8 @@
       <c r="G9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>0</v>
@@ -858,10 +850,8 @@
       <c r="G10" s="3" t="n">
         <v>0.015999</v>
       </c>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H10" s="3" t="n">
+        <v>0.004358</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.09045499999999999</v>
@@ -958,10 +948,8 @@
       <c r="G12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1003,10 +991,8 @@
       <c r="G13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>-0</v>
@@ -1048,10 +1034,8 @@
       <c r="G14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0</v>
@@ -1093,10 +1077,8 @@
       <c r="G15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>0</v>
@@ -1138,10 +1120,8 @@
       <c r="G16" s="3" t="n">
         <v>-0.026921</v>
       </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H16" s="3" t="n">
+        <v>-0.043782</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.09586</v>
@@ -1183,10 +1163,8 @@
       <c r="G17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -1362,10 +1340,8 @@
       <c r="G20" s="3" t="n">
         <v>-0.026921</v>
       </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H20" s="3" t="n">
+        <v>-0.043782</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.09586</v>
@@ -1407,10 +1383,8 @@
       <c r="G21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
@@ -1452,10 +1426,8 @@
       <c r="G22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>0</v>
@@ -1497,10 +1469,8 @@
       <c r="G23" s="3" t="n">
         <v>-0.026921</v>
       </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H23" s="3" t="n">
+        <v>-0.043782</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.09586</v>
@@ -1542,10 +1512,8 @@
       <c r="G24" s="3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="H24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H24" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>-0.03</v>
@@ -1587,10 +1555,8 @@
       <c r="G25" s="3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="H25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H25" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>-0.03</v>
@@ -1695,10 +1661,8 @@
       <c r="G27" s="3" t="n">
         <v>-0.026921</v>
       </c>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H27" s="3" t="n">
+        <v>-0.043782</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.09586</v>
@@ -1740,10 +1704,8 @@
       <c r="G28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0</v>
@@ -1785,10 +1747,8 @@
       <c r="G29" s="3" t="n">
         <v>-0.026921</v>
       </c>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H29" s="3" t="n">
+        <v>-0.043782</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.09586</v>
@@ -1897,10 +1857,8 @@
       <c r="G31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="H31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -5039,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004358</v>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
@@ -5264,7 +5222,7 @@
         <v>-0.007953999999999999</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.037135</v>
+        <v>0.032777</v>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
@@ -6633,7 +6591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P220"/>
+  <dimension ref="A1:P249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15163,7 +15121,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Net loss for the year $ (48,116) $</t>
+          <t>Net loss for the year $ (95,860) $</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -15192,18 +15150,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J113" s="5" t="n">
-        <v>-0.043782</v>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L113" s="5" t="n">
+        <v>-0.048116</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -15239,7 +15197,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Write-down on sales tax receivable 818</t>
+          <t>Write-down on sales tax receivable 5,405</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -15268,18 +15226,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J114" s="5" t="n">
-        <v>0.004358</v>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L114" s="5" t="n">
+        <v>0.000818</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -15315,10 +15273,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GST Receivable -</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities (239,621)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -15344,18 +15306,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J115" s="5" t="n">
-        <v>-0.004358</v>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L115" s="5" t="n">
+        <v>0.046789</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -15391,12 +15353,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 46,789</t>
+          <t>Net cash used in operating activities (330,076)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -15424,18 +15386,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J116" s="5" t="n">
-        <v>0.037135</v>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L116" s="5" t="n">
+        <v>-0.000509</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -15466,19 +15428,15 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Change in non-cash operating working capital</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities (509)</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Proceeds from promissory note 102,008</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -15504,8 +15462,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J117" s="5" t="n">
-        <v>-0.006647</v>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -15551,7 +15511,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Advances from related party -</t>
+          <t>Repayment of promissory note (102,008)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -15580,8 +15540,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J118" s="5" t="n">
-        <v>0.001379</v>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -15627,12 +15589,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities -</t>
+          <t>Issuance of common shares 400,000</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -15660,8 +15622,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J119" s="5" t="n">
-        <v>0.001379</v>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -15707,12 +15671,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Change in cash for the year (509)</t>
+          <t>Net cash provided by financing activities 400,000</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -15740,8 +15704,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J120" s="5" t="n">
-        <v>-0.005268</v>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -15787,10 +15753,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cash (overdraft), beginning of the year (173)</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+          <t>Change in cash for the year 69,924</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -15816,18 +15786,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J121" s="5" t="n">
-        <v>0.005095</v>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L121" s="5" t="n">
+        <v>-0.000509</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -15863,7 +15833,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cash (overdraft), end of the year $ (682) $</t>
+          <t>Cash (overdraft), beginning of the year (682)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -15892,18 +15862,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J122" s="5" t="n">
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="5" t="n">
         <v>-0.000173</v>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -15934,12 +15904,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Number    Amount   Contributed Surplus       Deficit            Deficiency</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Balance, May 31, 2018 4,866,749 203,016 82,364 (448,764)</t>
+          <t>Cash (overdraft), end of the year $ 69,242 $</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -15968,18 +15938,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J123" s="5" t="n">
-        <v>-0.163384</v>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L123" s="5" t="n">
+        <v>-0.000682</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -16010,15 +15980,19 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Number    Amount   Contributed Surplus       Deficit            Deficiency</t>
+          <t>Supplementary information with respect to cash flows</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Net loss - - - (43,782)</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t>Interest paid $ 4,948 $</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -16044,8 +16018,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J124" s="5" t="n">
-        <v>-0.043782</v>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -16086,12 +16062,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Number    Amount   Contributed Surplus       Deficit            Deficiency</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Balance, May 31, 2019 4,866,749 203,016 82,364 (492,546)</t>
+          <t>Net loss for the year $ (48,116) $</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -16121,7 +16097,7 @@
         </is>
       </c>
       <c r="J125" s="5" t="n">
-        <v>-0.207166</v>
+        <v>-0.043782</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -16162,12 +16138,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Number    Amount   Contributed Surplus       Deficit            Deficiency</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Net loss - - - (48,116)</t>
+          <t>Write-down on sales tax receivable 818</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -16197,7 +16173,7 @@
         </is>
       </c>
       <c r="J126" s="5" t="n">
-        <v>-0.048116</v>
+        <v>0.004358</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -16238,15 +16214,19 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Number    Amount   Contributed Surplus       Deficit            Deficiency</t>
+          <t>Change in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Balance, May 31, 2020 4,866,749 203,016 82,364 (540,662)</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
+          <t>GST Receivable -</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -16273,7 +16253,7 @@
         </is>
       </c>
       <c r="J127" s="5" t="n">
-        <v>-0.255282</v>
+        <v>-0.004358</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -16314,38 +16294,46 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Change in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Loss for the period $</t>
+          <t>Accounts payable and accrued liabilities 46,789</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="n">
-        <v>-0.060065</v>
-      </c>
-      <c r="F128" s="5" t="n">
-        <v>-0.172117</v>
-      </c>
-      <c r="G128" s="5" t="n">
-        <v>-0.057445</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I128" s="5" t="n">
-        <v>-0.032919</v>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J128" s="5" t="n">
-        <v>-0.026921</v>
+        <v>0.037135</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -16386,15 +16374,19 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Change in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Decrease (increase) in receivables and prepaid</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>Net cash used in operating activities (509)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -16410,14 +16402,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H129" s="5" t="n">
-        <v>0.008437999999999999</v>
-      </c>
-      <c r="I129" s="5" t="n">
-        <v>-0.002501</v>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J129" s="5" t="n">
-        <v>-0.001345</v>
+        <v>-0.006647</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -16458,19 +16454,15 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Decrease in accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Advances from related party -</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -16486,14 +16478,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H130" s="5" t="n">
-        <v>-0.002912</v>
-      </c>
-      <c r="I130" s="5" t="n">
-        <v>-0.007953999999999999</v>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J130" s="5" t="n">
-        <v>-0.000709</v>
+        <v>0.001379</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -16534,36 +16530,46 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Net cash provided by financing activities -</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E131" s="5" t="n">
-        <v>-0.064856</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>-0.159474</v>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>-0.028783</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>-0.030198</v>
-      </c>
-      <c r="I131" s="5" t="n">
-        <v>-0.040762</v>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J131" s="5" t="n">
-        <v>-0.02763</v>
+        <v>0.001379</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -16604,15 +16610,19 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Advances from related parties</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>Change in cash for the year (509)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -16628,14 +16638,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H132" s="5" t="n">
-        <v>0.0305</v>
-      </c>
-      <c r="I132" s="5" t="n">
-        <v>0.042</v>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J132" s="5" t="n">
-        <v>0.03</v>
+        <v>-0.005268</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -16676,19 +16690,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Cash (overdraft), beginning of the year (173)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -16704,14 +16714,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H133" s="5" t="n">
-        <v>0.0305</v>
-      </c>
-      <c r="I133" s="5" t="n">
-        <v>0.042</v>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J133" s="5" t="n">
-        <v>0.03</v>
+        <v>0.005095</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -16752,12 +16766,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Change in cash position for the year</t>
+          <t>Cash (overdraft), end of the year $ (682) $</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -16771,17 +16785,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G134" s="5" t="n">
-        <v>-0.028783</v>
-      </c>
-      <c r="H134" s="5" t="n">
-        <v>0.000302</v>
-      </c>
-      <c r="I134" s="5" t="n">
-        <v>0.001238</v>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J134" s="5" t="n">
-        <v>0.00237</v>
+        <v>-0.000173</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -16822,19 +16842,15 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Number    Amount   Contributed Surplus       Deficit            Deficiency</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Balance, May 31, 2018 4,866,749 203,016 82,364 (448,764)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -16855,11 +16871,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="5" t="n">
-        <v>0.001487</v>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J135" s="5" t="n">
-        <v>0.002725</v>
+        <v>-0.163384</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -16900,19 +16918,15 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Number    Amount   Contributed Surplus       Deficit            Deficiency</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cash, end of the year $</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Net loss - - - (43,782)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -16928,14 +16942,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H136" s="5" t="n">
-        <v>0.001487</v>
-      </c>
-      <c r="I136" s="5" t="n">
-        <v>0.002725</v>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J136" s="5" t="n">
-        <v>0.005095</v>
+        <v>-0.043782</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -16976,19 +16994,15 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Number    Amount   Contributed Surplus       Deficit            Deficiency</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Balance, May 31, 2019 4,866,749 203,016 82,364 (492,546)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -17004,16 +17018,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H137" s="5" t="n">
-        <v>-0.02866</v>
-      </c>
-      <c r="I137" s="5" t="n">
-        <v>-0.032919</v>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>-0.207166</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -17054,19 +17070,15 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Number    Amount   Contributed Surplus       Deficit            Deficiency</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Write-down on accounts payable</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Net loss - - - (48,116)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -17082,18 +17094,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H138" s="5" t="n">
-        <v>-0.01736</v>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J138" s="5" t="n">
+        <v>-0.048116</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -17134,19 +17146,15 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Number    Amount   Contributed Surplus       Deficit            Deficiency</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Balance, May 31, 2020 4,866,749 203,016 82,364 (540,662)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -17157,19 +17165,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G139" s="5" t="n">
-        <v>0.029968</v>
-      </c>
-      <c r="H139" s="5" t="n">
-        <v>0.001185</v>
-      </c>
-      <c r="I139" s="5" t="n">
-        <v>0.001487</v>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="n">
+        <v>-0.255282</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -17215,7 +17227,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Loss for the Year $</t>
+          <t>Loss for the period $</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17223,31 +17235,25 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E140" s="5" t="n">
+        <v>-0.060065</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>-0.172117</v>
       </c>
       <c r="G140" s="5" t="n">
         <v>-0.057445</v>
       </c>
-      <c r="H140" s="5" t="n">
-        <v>-0.02866</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>-0.032919</v>
+      </c>
+      <c r="J140" s="5" t="n">
+        <v>-0.026921</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -17288,19 +17294,15 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Write-down of accounts payable</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Decrease (increase) in receivables and prepaid</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -17317,17 +17319,13 @@
         </is>
       </c>
       <c r="H141" s="5" t="n">
-        <v>-0.01736</v>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.008437999999999999</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>-0.002501</v>
+      </c>
+      <c r="J141" s="5" t="n">
+        <v>-0.001345</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -17368,15 +17366,19 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Write-down of sales tax receivable</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
+          <t>Decrease in accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -17393,17 +17395,13 @@
         </is>
       </c>
       <c r="H142" s="5" t="n">
-        <v>0.010296</v>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.002912</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>-0.007953999999999999</v>
+      </c>
+      <c r="J142" s="5" t="n">
+        <v>-0.000709</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -17449,33 +17447,31 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Increase in receivables and prepaid</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>-0.064856</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>0.007784</v>
+        <v>-0.159474</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.005428</v>
+        <v>-0.028783</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>0.008437999999999999</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.030198</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>-0.040762</v>
+      </c>
+      <c r="J143" s="5" t="n">
+        <v>-0.02763</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -17516,40 +17512,38 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Increase in accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="n">
-        <v>0.000414</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>0.004859</v>
-      </c>
-      <c r="G144" s="5" t="n">
-        <v>0.023234</v>
+          <t>Advances from related parties</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H144" s="5" t="n">
-        <v>-0.002912</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0305</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J144" s="5" t="n">
+        <v>0.03</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -17595,12 +17589,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Cash, end of Year $</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -17613,21 +17607,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G145" s="5" t="n">
-        <v>0.001185</v>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H145" s="5" t="n">
-        <v>0.001487</v>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0305</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J145" s="5" t="n">
+        <v>0.03</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -17668,12 +17660,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cash received on acquisition of Sophia Capital Corp.</t>
+          <t>Change in cash position for the year</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -17682,28 +17674,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F146" s="5" t="n">
-        <v>0.040366</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>-0.028783</v>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>0.000302</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>0.001238</v>
+      </c>
+      <c r="J146" s="5" t="n">
+        <v>0.00237</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -17744,17 +17730,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Cash, beginning of the year</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -17762,8 +17748,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F147" s="5" t="n">
-        <v>0.040366</v>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -17775,15 +17763,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I147" s="5" t="n">
+        <v>0.001487</v>
+      </c>
+      <c r="J147" s="5" t="n">
+        <v>0.002725</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -17824,38 +17808,42 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Change in cash position for the period</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" s="5" t="n">
-        <v>-0.064856</v>
-      </c>
-      <c r="F148" s="5" t="n">
-        <v>-0.119108</v>
-      </c>
-      <c r="G148" s="5" t="n">
-        <v>-0.028783</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of the year $</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>0.001487</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>0.002725</v>
+      </c>
+      <c r="J148" s="5" t="n">
+        <v>0.005095</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -17896,37 +17884,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Loss for the year $</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="n">
-        <v>0.213932</v>
-      </c>
-      <c r="F149" s="5" t="n">
-        <v>0.149076</v>
-      </c>
-      <c r="G149" s="5" t="n">
-        <v>0.029968</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>-0.02866</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>-0.032919</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -17972,32 +17962,36 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
+          <t>Write-down on accounts payable</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E150" s="5" t="n">
-        <v>0.149076</v>
-      </c>
-      <c r="F150" s="5" t="n">
-        <v>0.029968</v>
-      </c>
-      <c r="G150" s="5" t="n">
-        <v>0.001185</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="n">
+        <v>-0.01736</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -18048,15 +18042,19 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Twelve             Fifteen months</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Cash paid for interest $</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -18067,20 +18065,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G151" s="5" t="n">
+        <v>0.029968</v>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>0.001185</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>0.001487</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -18126,15 +18118,19 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Twelve             Fifteen months</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cash paid for income taxes $</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Loss for the Year $</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -18145,15 +18141,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G152" s="5" t="n">
+        <v>-0.057445</v>
+      </c>
+      <c r="H152" s="5" t="n">
+        <v>-0.02866</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -18204,30 +18196,36 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Twelve             Fifteen months</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Twelve             Fifteen months total</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>Write-down of accounts payable</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F153" s="5" t="n">
-        <v>0.002014</v>
-      </c>
-      <c r="G153" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>-0.01736</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -18278,30 +18276,32 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Increase (decrease) in receivables and prepaid</t>
+          <t>Write-down of sales tax receivable</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
-      <c r="E154" s="5" t="n">
-        <v>-0.005205</v>
-      </c>
-      <c r="F154" s="5" t="n">
-        <v>0.007784</v>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H154" s="5" t="n">
+        <v>0.010296</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -18352,34 +18352,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES total</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E155" s="5" t="n">
-        <v>0.002013</v>
+          <t>Increase in receivables and prepaid</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F155" s="5" t="n">
-        <v>2.8e-05</v>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007784</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>0.005428</v>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>0.008437999999999999</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -18425,39 +18419,35 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Finance expense (Note 3 and 5) $</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="n">
+        <v>0.000414</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>0.004859</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.023234</v>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>-0.002912</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -18484,35 +18474,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N156" s="5" t="n">
-        <v>0.005378</v>
-      </c>
-      <c r="O156" s="5" t="n">
-        <v>0.011218</v>
-      </c>
-      <c r="P156" s="5" t="n">
-        <v>0.018848</v>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Cash, end of Year $</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -18525,15 +18521,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G157" s="5" t="n">
+        <v>0.001185</v>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>0.001487</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -18550,52 +18542,56 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L157" s="5" t="n">
-        <v>-0.0006579999999999999</v>
-      </c>
-      <c r="M157" s="5" t="n">
-        <v>9.6e-05</v>
-      </c>
-      <c r="N157" s="5" t="n">
-        <v>7.1e-05</v>
-      </c>
-      <c r="O157" s="5" t="n">
-        <v>7.4e-05</v>
-      </c>
-      <c r="P157" s="5" t="n">
-        <v>7.1e-05</v>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Cash received on acquisition of Sophia Capital Corp.</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F158" s="5" t="n">
+        <v>0.040366</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -18622,41 +18618,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L158" s="5" t="n">
-        <v>0.068107</v>
-      </c>
-      <c r="M158" s="5" t="n">
-        <v>0.059865</v>
-      </c>
-      <c r="N158" s="5" t="n">
-        <v>0.049952</v>
-      </c>
-      <c r="O158" s="5" t="n">
-        <v>0.042482</v>
-      </c>
-      <c r="P158" s="5" t="n">
-        <v>0.045751</v>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -18664,10 +18670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F159" s="5" t="n">
+        <v>0.040366</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -18694,57 +18698,57 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L159" s="5" t="n">
-        <v>0.018058</v>
-      </c>
-      <c r="M159" s="5" t="n">
-        <v>0.017354</v>
-      </c>
-      <c r="N159" s="5" t="n">
-        <v>0.012362</v>
-      </c>
-      <c r="O159" s="5" t="n">
-        <v>0.015766</v>
-      </c>
-      <c r="P159" s="5" t="n">
-        <v>0.011082</v>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>TOTAL OPERATING EXPENSES</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash position for the period</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" s="5" t="n">
+        <v>-0.064856</v>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>-0.119108</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>-0.028783</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -18766,53 +18770,61 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L160" s="5" t="n">
-        <v>0.09045499999999999</v>
-      </c>
-      <c r="M160" s="5" t="n">
-        <v>0.07731499999999999</v>
-      </c>
-      <c r="N160" s="5" t="n">
-        <v>0.067763</v>
-      </c>
-      <c r="O160" s="5" t="n">
-        <v>0.06954</v>
-      </c>
-      <c r="P160" s="5" t="n">
-        <v>0.075752</v>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Loss on uncollectible sales tax receivable</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="n">
+        <v>0.213932</v>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>0.149076</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0.029968</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -18849,48 +18861,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O161" s="5" t="n">
-        <v>-0.002817</v>
-      </c>
-      <c r="P161" s="5" t="n">
-        <v>-0.002531</v>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
+          <t>Cash, end of period $</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="n">
+        <v>0.149076</v>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>0.029968</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.001185</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -18912,43 +18922,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L162" s="5" t="n">
-        <v>0.005405</v>
-      </c>
-      <c r="M162" s="5" t="n">
-        <v>0.003444</v>
-      </c>
-      <c r="N162" s="5" t="n">
-        <v>0.002945</v>
-      </c>
-      <c r="O162" s="5" t="n">
-        <v>0.002817</v>
-      </c>
-      <c r="P162" s="5" t="n">
-        <v>0.002531</v>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Twelve             Fifteen months</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Cash paid for interest $</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -18984,43 +19000,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L163" s="5" t="n">
-        <v>-0.09586</v>
-      </c>
-      <c r="M163" s="5" t="n">
-        <v>-0.080759</v>
-      </c>
-      <c r="N163" s="5" t="n">
-        <v>-0.07070799999999999</v>
-      </c>
-      <c r="O163" s="5" t="n">
-        <v>-0.072357</v>
-      </c>
-      <c r="P163" s="5" t="n">
-        <v>-0.07828300000000001</v>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Twelve             Fifteen months</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>BASIC AND DILUTED LOSS PER SHARE (Note 7) $</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Cash paid for income taxes $</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -19066,30 +19088,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N164" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="O164" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="P164" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES OUTSTANDING</t>
+          <t>Twelve             Fifteen months</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>(Basic and Diluted) (Note 7)</t>
+          <t>Twelve             Fifteen months total</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -19098,15 +19126,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F165" s="5" t="n">
+        <v>0.002014</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19138,42 +19162,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N165" s="5" t="n">
-        <v>9.107250000000001</v>
-      </c>
-      <c r="O165" s="5" t="n">
-        <v>9.107250000000001</v>
-      </c>
-      <c r="P165" s="5" t="n">
-        <v>9.107250000000001</v>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Write-down on sales tax receivable</t>
+          <t>Increase (decrease) in receivables and prepaid</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E166" s="5" t="n">
+        <v>-0.005205</v>
+      </c>
+      <c r="F166" s="5" t="n">
+        <v>0.007784</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -19200,17 +19226,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L166" s="5" t="n">
-        <v>-0.005405</v>
-      </c>
-      <c r="M166" s="5" t="n">
-        <v>-0.003444</v>
-      </c>
-      <c r="N166" s="5" t="n">
-        <v>-0.002945</v>
-      </c>
-      <c r="O166" s="5" t="n">
-        <v>-0.002817</v>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
@@ -19221,29 +19255,29 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Finance expense $</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES total</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="n">
+        <v>0.002013</v>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>2.8e-05</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -19270,8 +19304,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L167" s="5" t="n">
-        <v>0.004948</v>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -19307,14 +19343,10 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>BASIC AND DILUTED LOSS PER SHARE (Note 6) $</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Finance expense (Note 3 and 5) $</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -19350,26 +19382,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L168" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="M168" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="5" t="n">
+        <v>0.005378</v>
+      </c>
+      <c r="O168" s="5" t="n">
+        <v>0.011218</v>
+      </c>
+      <c r="P168" s="5" t="n">
+        <v>0.018848</v>
       </c>
     </row>
     <row r="169">
@@ -19380,15 +19410,19 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES OUTSTANDING 1</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>(Basic and Diluted) (Note 6)</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -19425,25 +19459,19 @@
         </is>
       </c>
       <c r="L169" s="5" t="n">
-        <v>3.524832</v>
+        <v>-0.0006579999999999999</v>
       </c>
       <c r="M169" s="5" t="n">
-        <v>9.107250000000001</v>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.6e-05</v>
+      </c>
+      <c r="N169" s="5" t="n">
+        <v>7.1e-05</v>
+      </c>
+      <c r="O169" s="5" t="n">
+        <v>7.4e-05</v>
+      </c>
+      <c r="P169" s="5" t="n">
+        <v>7.1e-05</v>
       </c>
     </row>
     <row r="170">
@@ -19452,13 +19480,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>For the years ended May</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -19495,27 +19531,19 @@
         </is>
       </c>
       <c r="L170" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.068107</v>
+      </c>
+      <c r="M170" s="5" t="n">
+        <v>0.059865</v>
+      </c>
+      <c r="N170" s="5" t="n">
+        <v>0.049952</v>
+      </c>
+      <c r="O170" s="5" t="n">
+        <v>0.042482</v>
+      </c>
+      <c r="P170" s="5" t="n">
+        <v>0.045751</v>
       </c>
     </row>
     <row r="171">
@@ -19531,10 +19559,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Finance expense (Note 4) $ 4,948 $</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -19570,30 +19602,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L171" s="5" t="n">
+        <v>0.018058</v>
+      </c>
+      <c r="M171" s="5" t="n">
+        <v>0.017354</v>
+      </c>
+      <c r="N171" s="5" t="n">
+        <v>0.012362</v>
+      </c>
+      <c r="O171" s="5" t="n">
+        <v>0.015766</v>
+      </c>
+      <c r="P171" s="5" t="n">
+        <v>0.011082</v>
       </c>
     </row>
     <row r="172">
@@ -19609,12 +19631,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>General and administrative (658)</t>
+          <t>TOTAL OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -19653,27 +19675,19 @@
         </is>
       </c>
       <c r="L172" s="5" t="n">
-        <v>0.000509</v>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.09045499999999999</v>
+      </c>
+      <c r="M172" s="5" t="n">
+        <v>0.07731499999999999</v>
+      </c>
+      <c r="N172" s="5" t="n">
+        <v>0.067763</v>
+      </c>
+      <c r="O172" s="5" t="n">
+        <v>0.06954</v>
+      </c>
+      <c r="P172" s="5" t="n">
+        <v>0.075752</v>
       </c>
     </row>
     <row r="173">
@@ -19689,14 +19703,10 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Professional fees 68,107</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Loss on uncollectible sales tax receivable</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -19732,8 +19742,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L173" s="5" t="n">
-        <v>0.008888</v>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -19745,15 +19757,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O173" s="5" t="n">
+        <v>-0.002817</v>
+      </c>
+      <c r="P173" s="5" t="n">
+        <v>-0.002531</v>
       </c>
     </row>
     <row r="174">
@@ -19769,12 +19777,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees 18,058</t>
+          <t>EXPENSES total</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -19807,33 +19815,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K174" s="5" t="n">
+        <v>0.004358</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>0.037901</v>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005405</v>
+      </c>
+      <c r="M174" s="5" t="n">
+        <v>0.003444</v>
+      </c>
+      <c r="N174" s="5" t="n">
+        <v>0.002945</v>
+      </c>
+      <c r="O174" s="5" t="n">
+        <v>0.002817</v>
+      </c>
+      <c r="P174" s="5" t="n">
+        <v>0.002531</v>
       </c>
     </row>
     <row r="175">
@@ -19849,10 +19847,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>TOTAL OPERATING EXPENSES (90,455)</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -19889,27 +19891,19 @@
         </is>
       </c>
       <c r="L175" s="5" t="n">
-        <v>-0.047298</v>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.09586</v>
+      </c>
+      <c r="M175" s="5" t="n">
+        <v>-0.080759</v>
+      </c>
+      <c r="N175" s="5" t="n">
+        <v>-0.07070799999999999</v>
+      </c>
+      <c r="O175" s="5" t="n">
+        <v>-0.072357</v>
+      </c>
+      <c r="P175" s="5" t="n">
+        <v>-0.07828300000000001</v>
       </c>
     </row>
     <row r="176">
@@ -19925,10 +19919,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Write-down on sales tax receivable (5,405)</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>BASIC AND DILUTED LOSS PER SHARE (Note 7) $</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -19964,28 +19962,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L176" s="5" t="n">
-        <v>-0.000818</v>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N176" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="O176" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="P176" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="177">
@@ -19996,19 +19990,15 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $ (95,860) $</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>(Basic and Diluted) (Note 7)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -20044,28 +20034,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L177" s="5" t="n">
-        <v>-0.048116</v>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N177" s="5" t="n">
+        <v>9.107250000000001</v>
+      </c>
+      <c r="O177" s="5" t="n">
+        <v>9.107250000000001</v>
+      </c>
+      <c r="P177" s="5" t="n">
+        <v>9.107250000000001</v>
       </c>
     </row>
     <row r="178">
@@ -20081,14 +20067,10 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BASIC AND DILUTED LOSS PER SHARE (Note 7) $ (0.03) $</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Write-down on sales tax receivable</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -20125,22 +20107,16 @@
         </is>
       </c>
       <c r="L178" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.005405</v>
+      </c>
+      <c r="M178" s="5" t="n">
+        <v>-0.003444</v>
+      </c>
+      <c r="N178" s="5" t="n">
+        <v>-0.002945</v>
+      </c>
+      <c r="O178" s="5" t="n">
+        <v>-0.002817</v>
       </c>
       <c r="P178" t="inlineStr">
         <is>
@@ -20154,14 +20130,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES OUTSTANDING1</t>
-        </is>
-      </c>
+      <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
-          <t>(Basic and Diluted) (Note 7) 3,524,832</t>
+          <t>For the years ended May</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -20195,23 +20167,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K179" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="L179" s="5" t="n">
-        <v>1.10725</v>
+        <v>3.1e-05</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N179" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
@@ -20232,32 +20200,44 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>General and administrative fees $</t>
+          <t>Finance expense (Note 3 and 5) $ 5,378 $</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" s="5" t="n">
-        <v>0.009174</v>
-      </c>
-      <c r="F180" s="5" t="n">
-        <v>0.025307</v>
-      </c>
-      <c r="G180" s="5" t="n">
-        <v>0.019314</v>
-      </c>
-      <c r="H180" s="5" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="I180" s="5" t="n">
-        <v>0.000472</v>
-      </c>
-      <c r="J180" s="5" t="n">
-        <v>0.000494</v>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -20298,36 +20278,48 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>General and administrative 71</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E181" s="5" t="n">
-        <v>0.03566</v>
-      </c>
-      <c r="F181" s="5" t="n">
-        <v>0.088684</v>
-      </c>
-      <c r="G181" s="5" t="n">
-        <v>0.019803</v>
-      </c>
-      <c r="H181" s="5" t="n">
-        <v>0.016663</v>
-      </c>
-      <c r="I181" s="5" t="n">
-        <v>0.011213</v>
-      </c>
-      <c r="J181" s="5" t="n">
-        <v>0.009083000000000001</v>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -20344,10 +20336,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N181" s="5" t="n">
+        <v>9.6e-05</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -20368,36 +20358,48 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
+          <t>Professional fees 49,952</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E182" s="5" t="n">
-        <v>0.015231</v>
-      </c>
-      <c r="F182" s="5" t="n">
-        <v>0.026142</v>
-      </c>
-      <c r="G182" s="5" t="n">
-        <v>0.018328</v>
-      </c>
-      <c r="H182" s="5" t="n">
-        <v>0.018661</v>
-      </c>
-      <c r="I182" s="5" t="n">
-        <v>0.018622</v>
-      </c>
-      <c r="J182" s="5" t="n">
-        <v>0.015999</v>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -20414,10 +20416,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N182" s="5" t="n">
+        <v>0.059865</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
@@ -20438,17 +20438,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss from operations $</t>
+          <t>Transfer agent and filing fees 12,362</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -20456,20 +20456,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F183" s="5" t="n">
-        <v>-0.140133</v>
-      </c>
-      <c r="G183" s="5" t="n">
-        <v>-0.057445</v>
-      </c>
-      <c r="H183" s="5" t="n">
-        <v>-0.035724</v>
-      </c>
-      <c r="I183" s="5" t="n">
-        <v>-0.030307</v>
-      </c>
-      <c r="J183" s="5" t="n">
-        <v>-0.025576</v>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -20486,10 +20496,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N183" s="5" t="n">
+        <v>0.017354</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
@@ -20510,12 +20518,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Write-down on sales tax receivable</t>
+          <t>TOTAL OPERATING EXPENSES (67,763)</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -20534,14 +20542,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H184" s="5" t="n">
-        <v>-0.010296</v>
-      </c>
-      <c r="I184" s="5" t="n">
-        <v>-0.002612</v>
-      </c>
-      <c r="J184" s="5" t="n">
-        <v>-0.001345</v>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -20558,10 +20572,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N184" s="5" t="n">
+        <v>-0.07731499999999999</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -20582,19 +20594,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Net Loss for the year $</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-down on sales tax receivable (2,945)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -20610,14 +20618,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H185" s="5" t="n">
-        <v>-0.02866</v>
-      </c>
-      <c r="I185" s="5" t="n">
-        <v>-0.032919</v>
-      </c>
-      <c r="J185" s="5" t="n">
-        <v>-0.026921</v>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -20634,10 +20648,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N185" s="5" t="n">
+        <v>-0.003444</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -20658,36 +20670,48 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $ (70,708) $</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E186" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="F186" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="G186" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="H186" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="I186" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="J186" s="5" t="n">
-        <v>-1e-08</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -20704,10 +20728,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N186" s="5" t="n">
+        <v>-0.080759</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
@@ -20728,36 +20750,48 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>BASIC AND DILUTED LOSS PER SHARE (Note 7) $ (0.01) $</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E187" s="5" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="F187" s="5" t="n">
-        <v>5.452848</v>
-      </c>
-      <c r="G187" s="5" t="n">
-        <v>5.390037</v>
-      </c>
-      <c r="H187" s="5" t="n">
-        <v>4.866749</v>
-      </c>
-      <c r="I187" s="5" t="n">
-        <v>4.866749</v>
-      </c>
-      <c r="J187" s="5" t="n">
-        <v>4.866749</v>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -20774,10 +20808,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N187" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
@@ -20798,12 +20830,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Balance, beginning of the year $</t>
+          <t>(Basic and Diluted) (Note 7) 9,107,250</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -20822,14 +20854,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H188" s="5" t="n">
-        <v>0.203016</v>
-      </c>
-      <c r="I188" s="5" t="n">
-        <v>0.203016</v>
-      </c>
-      <c r="J188" s="5" t="n">
-        <v>0.203016</v>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -20846,10 +20884,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N188" s="5" t="n">
+        <v>9.107250000000001</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
@@ -20870,12 +20906,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Balance, end of the year</t>
+          <t>Finance expense $</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -20894,24 +20930,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H189" s="5" t="n">
-        <v>0.203016</v>
-      </c>
-      <c r="I189" s="5" t="n">
-        <v>0.203016</v>
-      </c>
-      <c r="J189" s="5" t="n">
-        <v>0.203016</v>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L189" s="5" t="n">
+        <v>0.004948</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
@@ -20942,15 +20982,19 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Balance, beginning of the year</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>BASIC AND DILUTED LOSS PER SHARE (Note 6) $</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -20966,29 +21010,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H190" s="5" t="n">
-        <v>0.08236400000000001</v>
-      </c>
-      <c r="I190" s="5" t="n">
-        <v>0.08236400000000001</v>
-      </c>
-      <c r="J190" s="5" t="n">
-        <v>0.08236400000000001</v>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L190" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="M190" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="N190" t="inlineStr">
         <is>
@@ -21014,12 +21060,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES OUTSTANDING 1</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Balance, end of the year</t>
+          <t>(Basic and Diluted) (Note 6)</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -21038,29 +21084,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H191" s="5" t="n">
-        <v>0.08236400000000001</v>
-      </c>
-      <c r="I191" s="5" t="n">
-        <v>0.08236400000000001</v>
-      </c>
-      <c r="J191" s="5" t="n">
-        <v>0.08236400000000001</v>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L191" s="5" t="n">
+        <v>3.524832</v>
+      </c>
+      <c r="M191" s="5" t="n">
+        <v>9.107250000000001</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
@@ -21086,12 +21134,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Balance, beginning of the year</t>
+          <t>Finance expense (Note 4) $ 4,948 $</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -21110,14 +21158,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H192" s="5" t="n">
-        <v>-0.360264</v>
-      </c>
-      <c r="I192" s="5" t="n">
-        <v>-0.388924</v>
-      </c>
-      <c r="J192" s="5" t="n">
-        <v>-0.421843</v>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -21158,17 +21212,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>General and administrative (658)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -21191,21 +21245,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I193" s="5" t="n">
-        <v>-0.032919</v>
-      </c>
-      <c r="J193" s="5" t="n">
-        <v>-0.026921</v>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L193" s="5" t="n">
+        <v>0.000509</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
@@ -21236,15 +21292,19 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Balance, end of the year</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
+          <t>Professional fees 68,107</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -21260,24 +21320,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H194" s="5" t="n">
-        <v>-0.388924</v>
-      </c>
-      <c r="I194" s="5" t="n">
-        <v>-0.421843</v>
-      </c>
-      <c r="J194" s="5" t="n">
-        <v>-0.448764</v>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L194" s="5" t="n">
+        <v>0.008888</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
@@ -21308,15 +21372,19 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Total shareholders' deficiency $</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>Transfer agent and filing fees 18,058</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -21332,24 +21400,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H195" s="5" t="n">
-        <v>-0.103544</v>
-      </c>
-      <c r="I195" s="5" t="n">
-        <v>-0.136463</v>
-      </c>
-      <c r="J195" s="5" t="n">
-        <v>-0.163384</v>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L195" s="5" t="n">
+        <v>0.037901</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
@@ -21380,12 +21452,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Write-down on accounts payable</t>
+          <t>TOTAL OPERATING EXPENSES (90,455)</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -21404,8 +21476,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H196" s="5" t="n">
-        <v>0.01736</v>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -21422,10 +21496,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L196" s="5" t="n">
+        <v>-0.047298</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
@@ -21456,19 +21528,15 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Net loss for the period</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-down on sales tax receivable (5,405)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -21484,11 +21552,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H197" s="5" t="n">
-        <v>-0.02866</v>
-      </c>
-      <c r="I197" s="5" t="n">
-        <v>-0.032919</v>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -21500,10 +21572,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L197" s="5" t="n">
+        <v>-0.000818</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
@@ -21534,17 +21604,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Loss from operations $</t>
+          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $ (95,860) $</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -21557,11 +21627,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G198" s="5" t="n">
-        <v>-0.057445</v>
-      </c>
-      <c r="H198" s="5" t="n">
-        <v>-0.035724</v>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -21578,10 +21652,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L198" s="5" t="n">
+        <v>-0.048116</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
@@ -21612,15 +21684,19 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Write-down on sales tax receivable</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>BASIC AND DILUTED LOSS PER SHARE (Note 7) $ (0.03) $</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -21636,8 +21712,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H199" s="5" t="n">
-        <v>-0.010296</v>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -21654,10 +21732,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L199" s="5" t="n">
+        <v>-4e-08</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -21688,12 +21764,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES OUTSTANDING1</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Write-down on accounts payable</t>
+          <t>(Basic and Diluted) (Note 7) 3,524,832</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -21712,8 +21788,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H200" s="5" t="n">
-        <v>0.01736</v>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -21730,10 +21808,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L200" s="5" t="n">
+        <v>1.10725</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
@@ -21764,17 +21840,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period $</t>
+          <t>General and administrative $ 509 $</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -21787,11 +21863,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G201" s="5" t="n">
-        <v>-0.057445</v>
-      </c>
-      <c r="H201" s="5" t="n">
-        <v>-0.02866</v>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -21803,10 +21883,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K201" s="5" t="n">
+        <v>0.000392</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -21842,17 +21920,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Professional fees 8,888</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -21865,11 +21943,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G202" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="H202" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -21881,10 +21963,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K202" s="5" t="n">
+        <v>0.022789</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -21920,17 +22000,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Transfer agent and filing fees 37,901</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -21943,11 +22023,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G203" s="5" t="n">
-        <v>5.390037</v>
-      </c>
-      <c r="H203" s="5" t="n">
-        <v>4.866749</v>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -21959,10 +22043,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K203" s="5" t="n">
+        <v>0.016243</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -21998,12 +22080,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Shares      Amount      Reserves       Deficit       Deficiency</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Balance, May 31, 2014 5,866,749 $ 244,731 $ 40,649 $</t>
+          <t>TOTAL OPERATING EXPENSES (47,298)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -22017,11 +22099,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G204" s="5" t="n">
-        <v>-0.017439</v>
-      </c>
-      <c r="H204" s="5" t="n">
-        <v>-0.302819</v>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -22033,10 +22119,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K204" s="5" t="n">
+        <v>-0.039424</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -22072,19 +22156,15 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Shares      Amount      Reserves       Deficit       Deficiency</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss - - -</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-down on sales tax receivable (818)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -22095,11 +22175,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G205" s="5" t="n">
-        <v>-0.057445</v>
-      </c>
-      <c r="H205" s="5" t="n">
-        <v>-0.057445</v>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -22111,10 +22195,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K205" s="5" t="n">
+        <v>-0.004358</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -22150,15 +22232,19 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Shares      Amount      Reserves       Deficit       Deficiency</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Shares cancelled on trasfer to NEX (1,000,000) (41,715) 41,715</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
+          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $ (48,116) $</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -22189,10 +22275,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K206" s="5" t="n">
+        <v>-0.043782</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -22228,15 +22312,19 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Shares      Amount      Reserves       Deficit       Deficiency</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Balance, May 31, 2015 4,866,749 203,016 82,364</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
+          <t>BASIC AND DILUTED LOSS PER SHARE (Note 6) $ (0.01) $</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -22247,11 +22335,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G207" s="5" t="n">
-        <v>-0.07488400000000001</v>
-      </c>
-      <c r="H207" s="5" t="n">
-        <v>-0.360264</v>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -22263,10 +22355,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K207" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -22302,12 +22392,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Shares      Amount      Reserves       Deficit       Deficiency</t>
+          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Balance, May 31, 2016 4,866,749 $ 203,016 $ 82,364 $</t>
+          <t>(Basic and Diluted) (Note 6) 3,321,750</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -22321,11 +22411,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G208" s="5" t="n">
-        <v>-0.103544</v>
-      </c>
-      <c r="H208" s="5" t="n">
-        <v>-0.388924</v>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -22337,10 +22431,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K208" s="5" t="n">
+        <v>3.32175</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -22376,42 +22468,32 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Write-down on acquisition (Note 4)</t>
+          <t>General and administrative fees $</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E209" s="5" t="n">
+        <v>0.009174</v>
       </c>
       <c r="F209" s="5" t="n">
-        <v>-0.032036</v>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025307</v>
+      </c>
+      <c r="G209" s="5" t="n">
+        <v>0.019314</v>
+      </c>
+      <c r="H209" s="5" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>0.000472</v>
+      </c>
+      <c r="J209" s="5" t="n">
+        <v>0.000494</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -22452,46 +22534,36 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Interest and other income</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="n">
+        <v>0.03566</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>5.2e-05</v>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.088684</v>
+      </c>
+      <c r="G210" s="5" t="n">
+        <v>0.019803</v>
+      </c>
+      <c r="H210" s="5" t="n">
+        <v>0.016663</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>0.011213</v>
+      </c>
+      <c r="J210" s="5" t="n">
+        <v>0.009083000000000001</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -22532,44 +22604,36 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Net Loss for the period $</t>
+          <t>Transfer agent and filing fees</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="n">
+        <v>0.015231</v>
       </c>
       <c r="F211" s="5" t="n">
-        <v>-0.172117</v>
+        <v>0.026142</v>
       </c>
       <c r="G211" s="5" t="n">
-        <v>-0.057445</v>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.018328</v>
+      </c>
+      <c r="H211" s="5" t="n">
+        <v>0.018661</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>0.018622</v>
+      </c>
+      <c r="J211" s="5" t="n">
+        <v>0.015999</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -22610,40 +22674,38 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Shares      Amount      Reserves        Deficit     Equity (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Balance, February 28, 2013 4,150,000 $ 236,712 $ 40,649 $</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
+          <t>Loss and comprehensive loss from operations $</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.146659</v>
+        <v>-0.140133</v>
       </c>
       <c r="G212" s="5" t="n">
-        <v>-0.130702</v>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.057445</v>
+      </c>
+      <c r="H212" s="5" t="n">
+        <v>-0.035724</v>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>-0.030307</v>
+      </c>
+      <c r="J212" s="5" t="n">
+        <v>-0.025576</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
@@ -22684,44 +22746,38 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Shares      Amount      Reserves        Deficit     Equity (Deficiency)</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss - - -</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-down on sales tax receivable</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F213" s="5" t="n">
-        <v>-0.172117</v>
-      </c>
-      <c r="G213" s="5" t="n">
-        <v>-0.172117</v>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="n">
+        <v>-0.010296</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>-0.002612</v>
+      </c>
+      <c r="J213" s="5" t="n">
+        <v>-0.001345</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
@@ -22762,42 +22818,42 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Shares issued on acquisition of</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Sophia Capital Corp. 1,716,749 8,019 -</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr"/>
+          <t>Net Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F214" s="5" t="n">
-        <v>0.008019</v>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H214" s="5" t="n">
+        <v>-0.02866</v>
+      </c>
+      <c r="I214" s="5" t="n">
+        <v>-0.032919</v>
+      </c>
+      <c r="J214" s="5" t="n">
+        <v>-0.026921</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
@@ -22838,40 +22894,36 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Shares issued on acquisition of</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Balance, May 31, 2014 5,866,749 $ 244,731 $ 40,649 $</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="F215" s="5" t="n">
-        <v>-0.017439</v>
+        <v>-3e-08</v>
       </c>
       <c r="G215" s="5" t="n">
-        <v>-0.302819</v>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="H215" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="J215" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
@@ -22912,44 +22964,36 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Shares issued on acquisition of</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss - - -</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="n">
+        <v>4.15</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>-0.057445</v>
+        <v>5.452848</v>
       </c>
       <c r="G216" s="5" t="n">
-        <v>-0.057445</v>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.390037</v>
+      </c>
+      <c r="H216" s="5" t="n">
+        <v>4.866749</v>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>4.866749</v>
+      </c>
+      <c r="J216" s="5" t="n">
+        <v>4.866749</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -22990,12 +23034,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Shares issued on acquisition of</t>
+          <t>Share Capital</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Shares cancelled on trasfer to NEX (1,000,000) (41,715) 41,715</t>
+          <t>Balance, beginning of the year $</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -23014,20 +23058,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H217" s="5" t="n">
+        <v>0.203016</v>
+      </c>
+      <c r="I217" s="5" t="n">
+        <v>0.203016</v>
+      </c>
+      <c r="J217" s="5" t="n">
+        <v>0.203016</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -23068,12 +23106,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Shares issued on acquisition of</t>
+          <t>Share Capital</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Balance, May 31, 2015 4,866,749 $ 203,016 $ 82,364 $</t>
+          <t>Balance, end of the year</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -23082,26 +23120,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F218" s="5" t="n">
-        <v>-0.07488400000000001</v>
-      </c>
-      <c r="G218" s="5" t="n">
-        <v>-0.360264</v>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="n">
+        <v>0.203016</v>
+      </c>
+      <c r="I218" s="5" t="n">
+        <v>0.203016</v>
+      </c>
+      <c r="J218" s="5" t="n">
+        <v>0.203016</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -23142,44 +23178,38 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E219" s="5" t="n">
-        <v>0.060065</v>
-      </c>
-      <c r="F219" s="5" t="n">
-        <v>0.140133</v>
+          <t>Balance, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H219" s="5" t="n">
+        <v>0.08236400000000001</v>
+      </c>
+      <c r="I219" s="5" t="n">
+        <v>0.08236400000000001</v>
+      </c>
+      <c r="J219" s="5" t="n">
+        <v>0.08236400000000001</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -23220,71 +23250,2277 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
+          <t>Contributed surplus</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Balance, end of the year</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" s="5" t="n">
+        <v>0.08236400000000001</v>
+      </c>
+      <c r="I220" s="5" t="n">
+        <v>0.08236400000000001</v>
+      </c>
+      <c r="J220" s="5" t="n">
+        <v>0.08236400000000001</v>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Balance, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" s="5" t="n">
+        <v>-0.360264</v>
+      </c>
+      <c r="I221" s="5" t="n">
+        <v>-0.388924</v>
+      </c>
+      <c r="J221" s="5" t="n">
+        <v>-0.421843</v>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I222" s="5" t="n">
+        <v>-0.032919</v>
+      </c>
+      <c r="J222" s="5" t="n">
+        <v>-0.026921</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Balance, end of the year</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>-0.388924</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>-0.421843</v>
+      </c>
+      <c r="J223" s="5" t="n">
+        <v>-0.448764</v>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Total shareholders' deficiency $</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H224" s="5" t="n">
+        <v>-0.103544</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>-0.136463</v>
+      </c>
+      <c r="J224" s="5" t="n">
+        <v>-0.163384</v>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
           <t>Other Items</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Write-down on accounts payable</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H225" s="5" t="n">
+        <v>0.01736</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Net loss for the period</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" s="5" t="n">
+        <v>-0.02866</v>
+      </c>
+      <c r="I226" s="5" t="n">
+        <v>-0.032919</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Loss from operations $</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="n">
+        <v>-0.057445</v>
+      </c>
+      <c r="H227" s="5" t="n">
+        <v>-0.035724</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Write-down on sales tax receivable</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H228" s="5" t="n">
+        <v>-0.010296</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Write-down on accounts payable</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="n">
+        <v>0.01736</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G230" s="5" t="n">
+        <v>-0.057445</v>
+      </c>
+      <c r="H230" s="5" t="n">
+        <v>-0.02866</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G231" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H231" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G232" s="5" t="n">
+        <v>5.390037</v>
+      </c>
+      <c r="H232" s="5" t="n">
+        <v>4.866749</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Shares      Amount      Reserves       Deficit       Deficiency</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Balance, May 31, 2014 5,866,749 $ 244,731 $ 40,649 $</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="n">
+        <v>-0.017439</v>
+      </c>
+      <c r="H233" s="5" t="n">
+        <v>-0.302819</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Shares      Amount      Reserves       Deficit       Deficiency</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss - - -</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G234" s="5" t="n">
+        <v>-0.057445</v>
+      </c>
+      <c r="H234" s="5" t="n">
+        <v>-0.057445</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Shares      Amount      Reserves       Deficit       Deficiency</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Shares cancelled on trasfer to NEX (1,000,000) (41,715) 41,715</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Shares      Amount      Reserves       Deficit       Deficiency</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Balance, May 31, 2015 4,866,749 203,016 82,364</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G236" s="5" t="n">
+        <v>-0.07488400000000001</v>
+      </c>
+      <c r="H236" s="5" t="n">
+        <v>-0.360264</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Shares      Amount      Reserves       Deficit       Deficiency</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Balance, May 31, 2016 4,866,749 $ 203,016 $ 82,364 $</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="n">
+        <v>-0.103544</v>
+      </c>
+      <c r="H237" s="5" t="n">
+        <v>-0.388924</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Write-down on acquisition (Note 4)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F238" s="5" t="n">
+        <v>-0.032036</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Interest and other income</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="n">
+        <v>5.2e-05</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Net Loss for the period $</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F240" s="5" t="n">
+        <v>-0.172117</v>
+      </c>
+      <c r="G240" s="5" t="n">
+        <v>-0.057445</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Shares      Amount      Reserves        Deficit     Equity (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Balance, February 28, 2013 4,150,000 $ 236,712 $ 40,649 $</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F241" s="5" t="n">
+        <v>0.146659</v>
+      </c>
+      <c r="G241" s="5" t="n">
+        <v>-0.130702</v>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Shares      Amount      Reserves        Deficit     Equity (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss - - -</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F242" s="5" t="n">
+        <v>-0.172117</v>
+      </c>
+      <c r="G242" s="5" t="n">
+        <v>-0.172117</v>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Sophia Capital Corp. 1,716,749 8,019 -</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F243" s="5" t="n">
+        <v>0.008019</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Balance, May 31, 2014 5,866,749 $ 244,731 $ 40,649 $</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F244" s="5" t="n">
+        <v>-0.017439</v>
+      </c>
+      <c r="G244" s="5" t="n">
+        <v>-0.302819</v>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss - - -</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F245" s="5" t="n">
+        <v>-0.057445</v>
+      </c>
+      <c r="G245" s="5" t="n">
+        <v>-0.057445</v>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Shares cancelled on trasfer to NEX (1,000,000) (41,715) 41,715</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Balance, May 31, 2015 4,866,749 $ 203,016 $ 82,364 $</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F247" s="5" t="n">
+        <v>-0.07488400000000001</v>
+      </c>
+      <c r="G247" s="5" t="n">
+        <v>-0.360264</v>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E248" s="5" t="n">
+        <v>0.060065</v>
+      </c>
+      <c r="F248" s="5" t="n">
+        <v>0.140133</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
         <is>
           <t>Loss for the period $</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D249" t="inlineStr">
         <is>
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E220" s="5" t="n">
+      <c r="E249" s="5" t="n">
         <v>-0.060065</v>
       </c>
-      <c r="F220" s="5" t="n">
+      <c r="F249" s="5" t="n">
         <v>-0.172117</v>
       </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P220" t="inlineStr">
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
         <is>
           <t>-</t>
         </is>
